--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -92,9 +92,6 @@
     <t>ELVIRA AGUILAR JULIO</t>
   </si>
   <si>
-    <t>GONZALEZ MARTINEZ LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>HERRERA XOTLANIHUA CELSO ALEJANDRO</t>
   </si>
   <si>
@@ -215,70 +212,112 @@
     <t>BERNABE</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CHULIN</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>ELVIRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NEPOMUCENO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>QUIJANO</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROSALIANO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NEPOMUCENO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
+    <t>MIXCOA</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>TZOPITL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
@@ -287,9 +326,6 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>ARELLANO</t>
   </si>
   <si>
@@ -302,30 +338,51 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAVARRO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>PIEDRAS</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>PEDRO EVER</t>
   </si>
   <si>
+    <t>NEIL</t>
+  </si>
+  <si>
     <t>IVAN</t>
   </si>
   <si>
+    <t>ANGEL ALDAIR</t>
+  </si>
+  <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
     <t>CESAR SAID</t>
   </si>
   <si>
@@ -335,7 +392,10 @@
     <t>JOSE MANUEL</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>CELSO ALEJANDRO</t>
   </si>
   <si>
     <t>PATRICIO</t>
@@ -362,103 +422,34 @@
     <t>ANGEL DANIEL</t>
   </si>
   <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
     <t>DIEGO HUMBERTO</t>
   </si>
   <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
     <t>SINAI ANTONIO</t>
   </si>
   <si>
+    <t>ZURIEL ELIHU</t>
+  </si>
+  <si>
     <t>JORGE MARIO</t>
   </si>
   <si>
+    <t>ARIEL CHARBEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>LUIS REY</t>
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
-  </si>
-  <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
   </si>
   <si>
     <t>DARINKA</t>
@@ -819,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -965,19 +956,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1010,7 +1001,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1027,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1042,19 +1033,19 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1081,13 +1072,13 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1119,19 +1110,19 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1167,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1181,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1196,19 +1187,19 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1232,16 +1223,16 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1273,19 +1264,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1309,16 +1300,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>6</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1335,7 +1326,7 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1350,19 +1341,19 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1389,16 +1380,16 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1427,19 +1418,19 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1466,10 +1457,10 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1489,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1504,19 +1495,19 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1540,13 +1531,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1566,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1581,19 +1572,19 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1620,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1629,7 +1620,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1643,7 +1634,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -1658,19 +1649,19 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1694,10 +1685,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1706,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1720,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1735,19 +1726,19 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1774,13 +1765,13 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1812,19 +1803,19 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1854,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1871,37 +1862,37 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1925,22 +1916,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1948,37 +1939,37 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>10</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2002,22 +1993,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2028,34 +2019,34 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2082,19 +2073,19 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2102,37 +2093,37 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>8</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2156,22 +2147,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2179,37 +2170,37 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2233,22 +2224,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2256,37 +2247,37 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2310,22 +2301,22 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2336,34 +2327,34 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>8</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2390,10 +2381,10 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2402,7 +2393,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,34 +2404,34 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>5</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>8</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2467,19 +2458,19 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2487,37 +2478,37 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>8</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2541,22 +2532,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2564,37 +2555,37 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>9</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2621,16 +2612,16 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2641,37 +2632,37 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>10</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2698,19 +2689,19 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2718,37 +2709,37 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>10</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2772,22 +2763,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2795,16 +2786,16 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>10</v>
@@ -2813,19 +2804,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2849,13 +2840,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2872,37 +2863,37 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29">
         <v>10</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2926,22 +2917,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2949,37 +2940,37 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>10</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3003,22 +2994,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3035,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -3044,19 +3035,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3089,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3103,37 +3094,37 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3157,22 +3148,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3183,34 +3174,34 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>10</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3234,22 +3225,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3257,37 +3248,37 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>10</v>
       </c>
       <c r="G34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3311,98 +3302,21 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35">
-        <v>10</v>
-      </c>
-      <c r="C35">
-        <v>6</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
-      </c>
-      <c r="E35">
-        <v>9</v>
-      </c>
-      <c r="F35">
-        <v>10</v>
-      </c>
-      <c r="G35">
-        <v>8</v>
-      </c>
-      <c r="H35">
-        <v>-1</v>
-      </c>
-      <c r="I35">
-        <v>-1</v>
-      </c>
-      <c r="J35">
-        <v>-1</v>
-      </c>
-      <c r="K35">
-        <v>-1</v>
-      </c>
-      <c r="L35">
-        <v>-1</v>
-      </c>
-      <c r="M35">
-        <v>-1</v>
-      </c>
-      <c r="N35">
-        <v>-1</v>
-      </c>
-      <c r="O35">
-        <v>-1</v>
-      </c>
-      <c r="P35">
-        <v>-1</v>
-      </c>
-      <c r="Q35">
-        <v>-1</v>
-      </c>
-      <c r="R35">
-        <v>-1</v>
-      </c>
-      <c r="S35">
-        <v>-1</v>
-      </c>
-      <c r="T35">
-        <v>10</v>
-      </c>
-      <c r="U35">
-        <v>6</v>
-      </c>
-      <c r="V35">
-        <v>6</v>
-      </c>
-      <c r="W35">
-        <v>9</v>
-      </c>
-      <c r="X35">
-        <v>10</v>
-      </c>
-      <c r="Y35">
         <v>8</v>
       </c>
     </row>
@@ -3430,31 +3344,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3462,31 +3376,31 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>37.5</v>
+        <v>58.06</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>41.94</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3494,22 +3408,22 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>71.88</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G3">
-        <v>28.13</v>
+        <v>19.35</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -3526,22 +3440,22 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -3558,25 +3472,25 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>28</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>9.68</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3590,25 +3504,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="G6">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3622,13 +3536,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3640,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3656,7 +3570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3665,422 +3579,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920186</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920188</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920190</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920192</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920193</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330061430023</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920195</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920197</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920198</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920199</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920200</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920201</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920202</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920203</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920205</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920207</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920209</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920212</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4090,7 +3604,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4099,373 +3613,373 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920186</v>
+        <v>21330051920185</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920188</v>
+        <v>21330051920186</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920190</v>
+        <v>21330051920187</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920192</v>
+        <v>21330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920193</v>
+        <v>21330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330061430023</v>
+        <v>21330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920195</v>
+        <v>21330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920197</v>
+        <v>21330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920386</v>
+        <v>21330051920193</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920198</v>
+        <v>19330061430023</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920199</v>
+        <v>21330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920200</v>
+        <v>21330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920201</v>
+        <v>21330051920197</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920202</v>
+        <v>21330051920386</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920203</v>
+        <v>21330051920198</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920205</v>
+        <v>21330051920199</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920207</v>
+        <v>21330051920200</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920209</v>
+        <v>21330051920201</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920212</v>
+        <v>21330051920202</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920213</v>
+        <v>21330051920203</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920185</v>
+        <v>21330051920204</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4473,16 +3987,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920187</v>
+        <v>21330051920205</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4490,16 +4004,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920189</v>
+        <v>21330051920206</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4507,16 +4021,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920191</v>
+        <v>21330051920207</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4524,16 +4038,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920194</v>
+        <v>21330051920208</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4541,16 +4055,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920196</v>
+        <v>21330051920209</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4558,16 +4072,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920204</v>
+        <v>21330051920210</v>
       </c>
       <c r="B28" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4575,16 +4089,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920206</v>
+        <v>21330051920211</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4592,16 +4106,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920208</v>
+        <v>21330051920212</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4609,16 +4123,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920210</v>
+        <v>21330051920213</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4626,35 +4140,18 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920211</v>
+        <v>21330051920214</v>
       </c>
       <c r="B32" t="s">
         <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051920214</v>
-      </c>
-      <c r="B33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" t="s">
-        <v>147</v>
-      </c>
-      <c r="E33">
         <v>0</v>
       </c>
     </row>
@@ -4665,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4674,22 +4171,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4700,22 +4197,22 @@
         <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4723,19 +4220,19 @@
         <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4743,45 +4240,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920195</v>
+        <v>21330051920202</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920195</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4789,45 +4286,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920202</v>
+        <v>21330051920192</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920202</v>
+        <v>21330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4835,45 +4332,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920203</v>
+        <v>21330051920386</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920203</v>
+        <v>21330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4881,45 +4378,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920213</v>
+        <v>21330051920201</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920213</v>
+        <v>21330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4927,232 +4424,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920186</v>
+        <v>21330051920213</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920190</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920192</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920199</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920201</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920205</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920207</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920209</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920212</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1048,7 +1048,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1202,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1279,7 +1279,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1356,7 +1356,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1433,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1510,7 +1510,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1664,7 +1664,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1741,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1818,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1895,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1972,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2126,7 +2126,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2203,7 +2203,7 @@
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2280,7 +2280,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2511,7 +2511,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2665,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2742,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2819,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2896,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2973,7 +2973,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3050,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3127,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3281,7 +3281,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3446,19 +3446,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G4">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4162,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4194,16 +4194,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330061430023</v>
+        <v>21330051920188</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4217,16 +4217,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330061430023</v>
+        <v>21330051920188</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4240,16 +4240,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920202</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920202</v>
+        <v>19330061430023</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4286,16 +4286,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920192</v>
+        <v>21330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4309,22 +4309,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920193</v>
+        <v>21330051920202</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920386</v>
+        <v>21330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4355,16 +4355,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920199</v>
+        <v>21330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4378,16 +4378,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920201</v>
+        <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4401,16 +4401,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920203</v>
+        <v>21330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4424,16 +4424,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920213</v>
+        <v>21330051920201</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4442,6 +4442,52 @@
         <v>52</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920203</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920213</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -980,13 +980,13 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -998,7 +998,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1057,13 +1057,13 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1134,13 +1134,13 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1211,7 +1211,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1288,13 +1288,13 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1365,13 +1365,13 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1383,13 +1383,13 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1442,13 +1442,13 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1519,13 +1519,13 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1673,13 +1673,13 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1691,13 +1691,13 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1750,13 +1750,13 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1827,13 +1827,13 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1904,13 +1904,13 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1981,13 +1981,13 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2005,7 +2005,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2058,7 +2058,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2135,13 +2135,13 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2153,13 +2153,13 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2212,7 +2212,7 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2289,13 +2289,13 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2313,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2366,7 +2366,7 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2443,13 +2443,13 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2461,13 +2461,13 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2520,13 +2520,13 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2538,7 +2538,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2597,13 +2597,13 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2621,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2674,13 +2674,13 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2751,13 +2751,13 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2828,13 +2828,13 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2846,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2905,13 +2905,13 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2923,13 +2923,13 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2982,13 +2982,13 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3059,13 +3059,13 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3136,13 +3136,13 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3154,13 +3154,13 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3213,7 +3213,7 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3290,13 +3290,13 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3414,19 +3414,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="G3">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4162,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920192</v>
+        <v>21330051920203</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920193</v>
+        <v>21330051920203</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4378,16 +4378,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920386</v>
+        <v>21330051920192</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4401,16 +4401,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920199</v>
+        <v>21330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4424,16 +4424,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920201</v>
+        <v>21330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4447,16 +4447,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920203</v>
+        <v>21330051920199</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4470,16 +4470,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920213</v>
+        <v>21330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -4488,6 +4488,29 @@
         <v>52</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920213</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -182,10 +182,10 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
@@ -974,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1051,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1128,7 +1128,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1223,7 +1223,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1282,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1359,7 +1359,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1436,7 +1436,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1513,7 +1513,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1590,7 +1590,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1667,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1744,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1821,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1898,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1916,7 +1916,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -2052,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2129,7 +2129,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2147,7 +2147,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2206,7 +2206,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2283,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2360,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2437,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2514,7 +2514,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2591,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2609,7 +2609,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2668,7 +2668,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2686,7 +2686,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2822,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2899,7 +2899,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2917,7 +2917,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -2976,7 +2976,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3053,7 +3053,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3071,7 +3071,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3130,7 +3130,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3148,7 +3148,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3207,7 +3207,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -3284,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3446,19 +3446,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>90.31999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G4">
-        <v>9.68</v>
+        <v>12.9</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3490,7 +3490,7 @@
         <v>9.68</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4162,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4194,16 +4194,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920188</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4217,16 +4217,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920188</v>
+        <v>19330061430023</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4240,16 +4240,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330061430023</v>
+        <v>21330051920202</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4286,16 +4286,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4309,16 +4309,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920203</v>
+        <v>21330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920203</v>
+        <v>21330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4378,16 +4378,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920192</v>
+        <v>21330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4401,16 +4401,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920193</v>
+        <v>21330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4424,16 +4424,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920386</v>
+        <v>21330051920201</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4447,16 +4447,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920199</v>
+        <v>21330051920213</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4465,52 +4465,6 @@
         <v>52</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920201</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920213</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -2218,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -3542,16 +3542,16 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H7">
         <v>8.9</v>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="145">
   <si>
     <t>Materia</t>
   </si>
@@ -185,13 +185,13 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Aurioles Maldonado Luis Gustavo</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
     <t>NC</t>
@@ -977,13 +977,13 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1054,13 +1054,13 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1208,16 +1208,16 @@
         <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1235,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1285,13 +1285,13 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1362,13 +1362,13 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>6</v>
@@ -1439,13 +1439,13 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1516,13 +1516,13 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1534,7 +1534,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1593,16 +1593,16 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1617,10 +1617,10 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1670,13 +1670,13 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1747,13 +1747,13 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1824,13 +1824,13 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1901,13 +1901,13 @@
         <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -1978,13 +1978,13 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>5</v>
@@ -2055,16 +2055,16 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2082,7 +2082,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2132,13 +2132,13 @@
         <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>5</v>
@@ -2209,13 +2209,13 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2286,13 +2286,13 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2304,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2363,16 +2363,16 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2381,7 +2381,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2390,7 +2390,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2440,13 +2440,13 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>5</v>
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2594,13 +2594,13 @@
         <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2671,13 +2671,13 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>6</v>
@@ -2748,13 +2748,13 @@
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2766,7 +2766,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2825,13 +2825,13 @@
         <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -2902,13 +2902,13 @@
         <v>5</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -2979,13 +2979,13 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
@@ -3056,13 +3056,13 @@
         <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3133,13 +3133,13 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>6</v>
@@ -3210,16 +3210,16 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3228,16 +3228,16 @@
         <v>6</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3287,13 +3287,13 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3382,19 +3382,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>58.06</v>
+        <v>70.97</v>
       </c>
       <c r="G2">
-        <v>41.94</v>
+        <v>29.03</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3478,19 +3478,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>90.31999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G5">
-        <v>9.68</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3501,7 +3501,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3510,19 +3510,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>96.77</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G6">
-        <v>3.23</v>
+        <v>9.68</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3554,7 +3554,7 @@
         <v>3.23</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4162,7 +4162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4240,16 +4240,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4263,16 +4263,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920202</v>
+        <v>21330051920203</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4286,16 +4286,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920203</v>
+        <v>21330051920193</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4309,22 +4309,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920203</v>
+        <v>21330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920192</v>
+        <v>21330051920199</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920193</v>
+        <v>21330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4378,93 +4378,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920386</v>
+        <v>21330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920199</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920201</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920213</v>
-      </c>
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20221.xlsx
+++ b/grupos/3BEM - Estadisticos 20221.xlsx
@@ -989,7 +989,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1143,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1238,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1297,7 +1297,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1528,7 +1528,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1546,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1605,7 +1605,7 @@
         <v>3</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1682,7 +1682,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1700,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1759,7 +1759,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1836,7 +1836,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1913,7 +1913,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1990,7 +1990,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -2008,7 +2008,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2067,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2162,7 +2162,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2298,7 +2298,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2316,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2375,7 +2375,7 @@
         <v>3</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2452,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2470,7 +2470,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2529,7 +2529,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2606,7 +2606,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2683,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2760,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2837,7 +2837,7 @@
         <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2914,7 +2914,7 @@
         <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2932,7 +2932,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2991,7 +2991,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3068,7 +3068,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3145,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3163,7 +3163,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3222,7 +3222,7 @@
         <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -3240,7 +3240,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3299,7 +3299,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3522,7 +3522,7 @@
         <v>9.68</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
